--- a/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
+++ b/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
@@ -12,22 +12,19 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Lot A - Forum" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Lot B - Pavilion" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Schedule" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Team" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Internal" sheetId="7" state="hidden" r:id="rId9"/>
+    <sheet name="Team" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Internal" sheetId="6" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$H$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Internal!$A$1:$G$27</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Lot A - Forum'!$A$1:$H$27</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Internal!$A$1:$G$29</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Lot A - Forum'!$A$1:$H$31</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Lot A - Forum'!$4:$4</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Lot B - Pavilion'!$A$1:$H$26</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Lot B - Pavilion'!$A$1:$H$21</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Lot B - Pavilion'!$4:$4</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Schedule!$A$1:$D$18</definedName>
-    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Schedule!$4:$4</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$F$36</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Team!$A$1:$C$18</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">Team!$4:$4</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$F$37</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Team!$A$1:$C$18</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">Team!$4:$4</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="219">
   <si>
     <t xml:space="preserve">COMMERCIAL PROPOSAL</t>
   </si>
@@ -75,10 +72,7 @@
     <t xml:space="preserve">PREPARED BY</t>
   </si>
   <si>
-    <t xml:space="preserve">Miradore Experiences — Riyadh, KSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhammad Usman Fiaz   ·   +966 54 803 6101   ·   1usmanfiaz@gmail.com</t>
+    <t xml:space="preserve">Miradore Experiences — Riyadh, Kingdom of Saudi Arabia</t>
   </si>
   <si>
     <t xml:space="preserve">Ref: MIR-PSEB-LEAP-2026-001        Date: 21 July 2026        Validity: 60 days</t>
@@ -93,7 +87,7 @@
     <t xml:space="preserve">Pakistan Saudi Business Forum (Lot A) · Pakistan Pavilion at LEAP 2026 (Lot B) · Riyadh, KSA</t>
   </si>
   <si>
-    <t xml:space="preserve">Miradore Experiences is pleased to submit this financial proposal for both lots of the PSEB RFQ. We will act as the single point of contact for end-to-end delivery: venue sourcing and advance-payment facilitation at Crowne Plaza Riyadh RDC for the 300-guest Business Forum, and turnkey design, fabrication, regulatory approvals, power, hospitality and multi-crew media coverage for the 162-SQM Pakistan Pavilion (Hall 3 — H170 / J170) at Riyadh Exhibition &amp; Convention Centre, Malham. Itemized unit rates are provided for every RFP line under each lot, as required.</t>
+    <t xml:space="preserve">Miradore Experiences is pleased to submit this financial proposal for both lots of the PSEB RFQ. Lot A covers the 300-guest Pakistan Saudi Business Forum at Crowne Plaza Riyadh RDC — the hotel venue &amp; catering package is passed through at actual cost, with all production, branding, AV, staging and media services itemized at unit rates. Lot B covers the 162-SQM Pakistan Pavilion at Riyadh Exhibition &amp; Convention Centre, Malham (Hall 3 — H170 / J170), offered as a single all-inclusive turnkey package (design, fabrication, approvals, power and installation) plus daily hospitality, provisioning, cleaning and multi-crew media coverage across all four LEAP days.</t>
   </si>
   <si>
     <t xml:space="preserve">COMMERCIAL PARAMETERS  (editable inputs)</t>
@@ -135,13 +129,13 @@
     <t xml:space="preserve">Lot A — Pakistan Saudi Business Forum (30 Aug 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal of itemized BOQ — see Lot A sheet</t>
+    <t xml:space="preserve">Incl. Crowne Plaza venue &amp; catering package at cost (325,000) + itemized production &amp; services</t>
   </si>
   <si>
     <t xml:space="preserve">Lot B — Pakistan Pavilion at LEAP 2026 (31 Aug – 3 Sep)</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal of itemized BOQ — see Lot B sheet</t>
+    <t xml:space="preserve">Turnkey pavilion package + LEAP-days services — see Lot B sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Combined Subtotal</t>
@@ -187,6 +181,9 @@
   </si>
   <si>
     <t xml:space="preserve">•  Payment strictly on actual basis post-event, upon successful delivery, verification and performance certification by PSEB (no advance payment), as per the RFP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  The Crowne Plaza Riyadh RDC venue &amp; catering package (Lot A, item A.1) is passed through at actual hotel package cost, with no markup.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Prices are quoted in Saudi Riyals (SAR); PKR equivalents are provided at the reference exchange rate stated above and will be aligned to the prevailing rate at invoicing.</t>
@@ -248,12 +245,27 @@
     <t xml:space="preserve">A.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Venue Booking for 30 Aug 2026 — Crowne Plaza Riyadh RDC Hotel: securing the venue for 300 guests on PSEB's behalf including all mandatory advance payments to hotel management, full seating arrangements, main stage (10m x 4m, carpeted), dedicated 5 Mbps internet line, and end-to-end hotel/banquet coordination with technical rehearsal.</t>
+    <t xml:space="preserve">Venue Booking for 30 Aug 2026 — Crowne Plaza Riyadh RDC Hotel: booking on PSEB's behalf and securing the venue by facilitating all mandatory advance payments required by hotel management. All-inclusive hotel package covering ballroom/hall space for 300 guests, 5-course continental buffet dinner with two coffee-break services, banquet seating &amp; tables, hotel service staff and dedicated 5 Mbps internet. Passed through at actual hotel package cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event Management, Production Planning, Venue Coordination &amp; Technical Rehearsal — end-to-end show management for the Forum.</t>
   </si>
   <si>
     <t xml:space="preserve">Job</t>
   </si>
   <si>
+    <t xml:space="preserve">A.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stage — portable stage 10m x 4m (40 sqm) with premium stage carpet and step access, as part of the main-stage arrangements under A.1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">A.2</t>
   </si>
   <si>
@@ -308,24 +320,36 @@
     <t xml:space="preserve">A.9</t>
   </si>
   <si>
-    <t xml:space="preserve">5-Course Continental Buffet Dinner for 300 participants with two coffee-break services, table service for the Minister and VVIP tables; menu options to be provided for PSEB approval.</t>
+    <t xml:space="preserve">5-Course Continental Buffet Dinner for 300 participants (buffet setup) with table service for the Minister and VVIP tables — included within the Crowne Plaza hotel package under A.1; menu options to be provided for PSEB approval.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included in A.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedicated on-site project coordinator liaising continuously with hotel banquet staff to ensure flawless event flow throughout the Forum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sourced Media Crew — one professional photography team and one videography team for complete event coverage, including: 100% raw photo/video upload to a shared secure Google Drive by midnight; polished 90-second highlight reel next day; ten short speaker/segment clips (15-sec and 30-sec variants) for social media next day; and a 3–5 minute high-production event documentary within 2 days of the Forum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional Ushers / Hostesses for guest management, registration support and VVIP handling.</t>
   </si>
   <si>
     <t xml:space="preserve">Person</t>
   </si>
   <si>
-    <t xml:space="preserve">A.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dedicated on-site project coordinator liaising continuously with hotel banquet staff to ensure flawless event flow throughout the Forum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sourced Media Crew — one professional photography team and one videography team for complete event coverage, including: 100% raw photo/video upload to a shared secure Google Drive by midnight; polished 90-second highlight reel next day; ten short speaker/segment clips (15-sec and 30-sec variants) for social media next day; and a 3–5 minute high-production event documentary within 2 days of the Forum.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subtotal</t>
   </si>
   <si>
@@ -338,10 +362,10 @@
     <t xml:space="preserve">LOT A — TOTAL (incl. VAT)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note 1: A.1 covers venue securing and advance-payment facilitation with Crowne Plaza Riyadh RDC on PSEB's behalf; banquet space is confirmed against the catering package in A.9.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note 2: A.9 rate is per person and includes the 5-course continental buffet dinner and two coffee-break services; final headcount will be billed on actuals as per PSEB confirmation.</t>
+    <t xml:space="preserve">Note 1: A.1 is the Crowne Plaza Riyadh RDC all-inclusive package (hall space + full catering for 300 guests) passed through at actual hotel package cost, with no markup.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note 2: A.9 (5-course continental buffet &amp; coffee breaks) is included within the A.1 hotel package; final headcount will be settled on actuals as per PSEB confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve">Note 3: All artwork and screen content will be produced by Miradore and released only after PSEB's written approval.</t>
@@ -353,40 +377,18 @@
     <t xml:space="preserve">Riyadh Exhibition &amp; Convention Centre (RECC), Malham · 31 Aug – 3 Sep 2026 · 162 SQM · Hall 3 (H170 / J170)</t>
   </si>
   <si>
-    <t xml:space="preserve">B.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turnkey Fabrication, Sourcing, Logistics &amp; Transportation of the 162-SQM Pakistan Pavilion (Hall 3 — Booths H170 / J170) across 3 blocks — workshop fabrication, safe transportation to RECC Malham, structural build per Annex I–III blueprints, on-site management and full dismantling/teardown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block A &amp; Block C Wood/MDF Build per Annex II — 16 booths (2 x 9-SQM and 6 x 6-SQM per block). Each booth fully fitted: 43" LED TV, branded info counter with die-cut logo, bar stool, 3 chairs and 1 round table, vinyl logo branding. Block branding: P2.6 LED screens (3.5m x 1m), backlit light boxes, neon accents, 3D acrylic + neon block logos, and premium wooden flooring with neon edge lighting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block B Premium Architectural Build per Annex III — 4 x 6-SQM booths, 30-SQM networking lounge and ministerial meeting room. Includes glass-walled meeting room (two 250cm x 240cm glass walls with glass door), 55" LED TV, two single-seater and one 2-seater sofas; per booth: 43" LED TV, branded counter, bar stool, 3 chairs, 1 round table and vinyl logos; lounge seating with round tables, P2.6 SMD screen, light boxes, 3D acrylic + neon logo and wooden flooring with neon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizer Stand-Build Permit, official stand audit approval, structural clearance and health/safety/security clearances for the entire pavilion, secured ahead of move-in deadlines.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Electrical Power Line Drops sourcing, supply and electrical panel deployment for Blocks A &amp; C (Annex II) and Block B (Annex III), engineered to run all SMDs, booth LCDs and lighting rigs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granular Exhibitor Booth Electrical Hookups — minimum 2 multi-pin power sockets per stall, meeting room and networking area (20 stalls + meeting room) for laptops, LEDs, mobiles, printers and related equipment.</t>
+    <t xml:space="preserve">B.1 – B.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURNKEY PAKISTAN PAVILION — ALL-INCLUSIVE PACKAGE (162 SQM · 3 Blocks · 20 Exhibitor Booths · 30-SQM Networking Lounge · Ministerial Meeting Room), built to Annex I–III blueprints &amp; specifications. Package includes:
+•  Design, fabrication, sourcing, logistics &amp; transportation to RECC Malham; structural build of Blocks A, B &amp; C; on-site management and full dismantling
+•  Block A &amp; C wood/MDF build (16 booths: 2 x 9-SQM + 6 x 6-SQM per block); Block B premium architectural build (4 x 6-SQM booths, lounge &amp; meeting room)
+•  Glass-walled ministerial meeting room (two 250cm x 240cm glass walls + glass door) with 55" LED TV, 2 single-seater and one 2-seater sofa
+•  P2.6 LED screens (3.5m x 1m) for block branding; 43" LED TV per booth; backlit light boxes; neon accent lighting; premium wooden flooring with neon edge
+•  3D acrylic + neon block logos, die-cut vinyl logos and full booth branding
+•  Branded info counter with bar stool, 3 chairs and 1 round table per booth; networking lounge seating with round tables
+•  Organizer stand-build permit, official stand audit approval, structural clearance and health/safety/security clearances ahead of move-in deadlines
+•  Main electrical power line drops, panel deployment and per-booth hookups — minimum 2 multi-pin power sockets in every booth, meeting room and networking area, engineered to run all SMDs, LCDs and lighting rigs</t>
   </si>
   <si>
     <t xml:space="preserve">B.7</t>
@@ -428,252 +430,84 @@
     <t xml:space="preserve">LOT B — TOTAL (incl. VAT)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note 1: B.1–B.6 together constitute the complete turnkey pavilion package (fabrication, logistics, build, approvals and power) per Annex I–III specifications — everything required to hand over a fully operational 162-SQM pavilion before move-in deadline.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note 2: A dedicated Project Manager and on-site coordination team (including tea servers) are deployed from project start for exhibitor coordination, booth design/artwork liaison and troubleshooting — included across B.1 and B.7.</t>
+    <t xml:space="preserve">Note 1: Line B.1 – B.6 consolidates the complete turnkey pavilion scope of the RFP (fabrication &amp; logistics, Block A &amp; C build, Block B build, organizer approvals &amp; clearances, main power supply and per-booth electrical hookups) as one all-inclusive package price — everything required to hand over a fully operational 162-SQM pavilion before the move-in deadline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note 2: A dedicated Project Manager and on-site coordination team (including tea servers) are deployed from project start for exhibitor coordination, booth design/artwork liaison and troubleshooting.</t>
   </si>
   <si>
     <t xml:space="preserve">Note 3: All raw footage, edits and creative assets are delivered as exclusive intellectual property of PSEB.</t>
   </si>
   <si>
-    <t xml:space="preserve">PROJECT DELIVERY SCHEDULE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granular fabrication, shipping, move-in, dry-run and teardown timeline — both lots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates (2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output / Milestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Award &amp; Kick-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 – 26 Jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract signing; dedicated PM assigned to PSEB; kick-off meeting; master production plan and approval calendar issued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signed work order; project plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design &amp; Approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 Jul – 8 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion shop drawings per Annex I–III; Forum stage/branding designs; all artwork routed for PSEB written approval; hotel contracting and advance payment to Crowne Plaza RDC to lock 30 Aug.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSEB-approved designs; venue secured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regulatory Clearances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 – 20 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stand-building permit submissions to LEAP organizer; structural calculations; stand audit approval; health, safety &amp; security clearances.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All permits &amp; audit approvals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 – 22 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshop fabrication of Blocks A, B &amp; C (wood/MDF, glass meeting room, counters, light boxes, 3D acrylic logos); procurement of LED/SMD, TVs, furniture and flooring.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion structures ready for QC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-Build &amp; QC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 – 25 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full pre-assembly and quality check at workshop; PSEB/client walkthrough (photos/video shared); snag rectification; packing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QC sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport &amp; Move-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 – 27 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safe transportation to RECC Malham; marshalling per organizer schedule; move-in and marking of Hall 3 (H170/J170).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materials on site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion Build</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27 – 29 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structural build of all 3 blocks; electrical main drops, panels and per-booth hookups; SMD/LED installation; branding; organizer stand audit inspection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion structurally complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum Setup &amp; Rehearsal</t>
+    <t xml:space="preserve">RESOURCE PLAN &amp; TALENT PROFILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedicated delivery team — single point of contact assigned exclusively to PSEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile &amp; Responsibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Director &amp; Client Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall engagement owner and commercial lead; direct escalation line for PSEB leadership; oversees both lots end-to-end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full engagement, pre-event &amp; on-site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedicated Project Manager (single point of contact for PSEB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assigned exclusively to PSEB for all pre-event and on-site liaison: exhibitor coordination, booth design &amp; artwork approvals, schedule control, daily progress reporting and troubleshooting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full-time from award to closeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Manager — Pavilion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leads fabrication, logistics and build of the 162-SQM pavilion; manages workshop, transport and RECC move-in/teardown per organizer schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrication through teardown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Supervisor &amp; Safety Officer — RECC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-floor supervision of build crews; compliance with organizer stand audit, structural and HSE requirements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move-in to teardown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certified Electrical Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main power drops, panel deployment and per-booth hookups per Annex II/III load metrics; on-call through all live days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build + 4 live days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV &amp; Technical Lead — Forum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD screens, mirror panels, sound and lighting systems at Crowne Plaza RDC; runs technical rehearsal and show calling.</t>
   </si>
   <si>
     <t xml:space="preserve">29 – 30 Aug</t>
   </si>
   <si>
-    <t xml:space="preserve">Overnight setup at Crowne Plaza RDC: stage, SMD screens, sound &amp; lighting, VVIP sofa layout, registration, media wall; full technical rehearsal morning of 30 Aug.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehearsal sign-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT — Business Forum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 Aug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pakistan Saudi Business Forum: 300 guests, keynotes, B2B, networking dinner; full media coverage; raw data uploaded by midnight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lot A delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion Dry-Run &amp; Handover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final snagging, content loading on all screens, cleaning, hospitality setup; pavilion handover to PSEB before LEAP opening.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavilion handover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVENT — LEAP 2026 Live Days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 Aug – 3 Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily operations: exhibitor support, tea/coffee station, lounge catering, water provisioning, continuous cleaning; 2+2 media crews; daily highlights and social clips per schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 live days delivered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teardown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 – 4 Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dismantling per organizer schedule, waste removal, material back-load, venue handback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean handback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 – 7 Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final pavilion documentary (within 2 days of close); Forum documentary; complete digital asset handover to PSEB; verification and performance certification support; final invoicing on actuals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closeout &amp; certification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESOURCE PLAN &amp; TALENT PROFILES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dedicated delivery team — single point of contact assigned exclusively to PSEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profile &amp; Responsibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Director &amp; Client Lead — Muhammad Usman Fiaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall engagement owner and commercial lead; direct escalation line for PSEB leadership; oversees both lots end-to-end. Contact: +966 54 803 6101 · 1usmanfiaz@gmail.com.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full engagement, pre-event &amp; on-site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dedicated Project Manager (single point of contact for PSEB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assigned exclusively to PSEB for all pre-event and on-site liaison: exhibitor coordination, booth design &amp; artwork approvals, schedule control, daily progress reporting and troubleshooting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full-time from award to closeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Manager — Pavilion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leads fabrication, logistics and build of the 162-SQM pavilion; manages workshop, transport and RECC move-in/teardown per organizer schedule.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrication through teardown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Supervisor &amp; Safety Officer — RECC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-floor supervision of build crews; compliance with organizer stand audit, structural and HSE requirements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move-in to teardown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Certified Electrical Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main power drops, panel deployment and per-booth hookups per Annex II/III load metrics; on-call through all live days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build + 4 live days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AV &amp; Technical Lead — Forum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD screens, mirror panels, sound and lighting systems at Crowne Plaza RDC; runs technical rehearsal and show calling.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Content Designer / Editor (2)</t>
   </si>
   <si>
@@ -743,10 +577,22 @@
     <t xml:space="preserve">Cost source</t>
   </si>
   <si>
-    <t xml:space="preserve">Venue booking + mgmt + stage + internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation BOQ: event mgmt 10,000 + stage &amp; carpet 7,400</t>
+    <t xml:space="preserve">Crowne Plaza package (hall + catering) — pass-through</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowne Plaza RDC offer: 325,000 + 15% VAT, incl. hall space, dinner + 2 coffee breaks (priced as-is, no markup)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event management &amp; technical rehearsal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation BOQ A.1 10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 10m x 4m + carpet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation BOQ A.8 5,600 + stage carpet 1,800</t>
   </si>
   <si>
     <t xml:space="preserve">VVIP 50 sofas + tables + florals</t>
@@ -797,12 +643,6 @@
     <t xml:space="preserve">Market estimate (not in supplier BOQ)</t>
   </si>
   <si>
-    <t xml:space="preserve">Buffet dinner 300 pax @325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crowne Plaza RDC: 325/pax + VAT, incl. dinner + 2 coffee breaks</t>
-  </si>
-  <si>
     <t xml:space="preserve">On-site project coordinator</t>
   </si>
   <si>
@@ -815,6 +655,12 @@
     <t xml:space="preserve">Innovation BOQ A.10 4,500 + editing/deliverables est. 1,500</t>
   </si>
   <si>
+    <t xml:space="preserve">Ushers x10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation BOQ A.11 10 x 650</t>
+  </si>
+  <si>
     <t xml:space="preserve">B.1-B.6</t>
   </si>
   <si>
@@ -857,10 +703,10 @@
     <t xml:space="preserve">TOTALS (excl. VAT, before agency commission)</t>
   </si>
   <si>
-    <t xml:space="preserve">Agency commission (12%) — additional revenue on top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions: hotel per-person cost 325 SAR + 15% VAT (dinner + 2 coffee breaks) per Crowne Plaza RDC offer relayed 18 Jul 2026; supplier costs from Innovation Events BOQ (WhatsApp, 18 Jul 2026) and Alpha Dimensions QUT-0126-26 (20 Jul 2026); 'est.' items are internal estimates. Costs above are excl. VAT; input VAT on supplier invoices is recoverable.</t>
+    <t xml:space="preserve">Agency commission (12% on lot subtotals) — additional revenue on top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions: Crowne Plaza RDC package 325,000 SAR + 15% VAT (hall + dinner + 2 coffee breaks, 300 pax) per offer relayed 18 Jul 2026, passed through at cost; supplier costs from Innovation Events BOQ (WhatsApp, 18 Jul 2026) and Alpha Dimensions QUT-0126-26 (20 Jul 2026); 'est.' items are internal estimates. Costs above are excl. VAT; input VAT on supplier invoices is recoverable.</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1045,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1296,36 +1142,40 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1333,7 +1183,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1345,7 +1195,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1369,7 +1219,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1392,6 +1242,18 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1424,10 +1286,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1440,7 +1298,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1449,7 +1307,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1457,14 +1315,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1489,6 +1339,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1963,29 +1817,19 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -2006,7 +1850,7 @@
       <c r="H36" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="B15:G15"/>
@@ -2019,8 +1863,7 @@
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B29:G29"/>
     <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B32:G32"/>
     <mergeCell ref="A35:H36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2039,7 +1882,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2051,7 +1894,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2061,7 +1904,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -2069,9 +1912,9 @@
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
     </row>
-    <row r="4" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -2079,7 +1922,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -2087,43 +1930,43 @@
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="20" t="n">
         <v>75.5</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -2131,127 +1974,127 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="D12" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="E12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="23" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="24" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="s">
+      <c r="C13" s="25" t="n">
+        <f aca="false">'Lot A - Forum'!F20</f>
+        <v>468350</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <f aca="false">ROUND(C13*Summary!$C$9,0)</f>
+        <v>35360425</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="24" t="n">
-        <f aca="false">'Lot A - Forum'!F17</f>
-        <v>253550</v>
-      </c>
-      <c r="D13" s="24" t="n">
-        <f aca="false">ROUND(C13*Summary!$C$9,0)</f>
-        <v>19143025</v>
-      </c>
-      <c r="E13" s="25" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="24" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">'Lot B - Pavilion'!F16</f>
+      <c r="C14" s="25" t="n">
+        <f aca="false">'Lot B - Pavilion'!F11</f>
         <v>317680</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <f aca="false">ROUND(C14*Summary!$C$9,0)</f>
         <v>23984840</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="27" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26" t="s">
+      <c r="C15" s="28" t="n">
+        <f aca="false">C13+C14</f>
+        <v>786030</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <f aca="false">ROUND(C15*Summary!$C$9,0)</f>
+        <v>59345265</v>
+      </c>
+      <c r="E15" s="29"/>
+    </row>
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <f aca="false">'Lot A - Forum'!F21+'Lot B - Pavilion'!F12</f>
+        <v>94323.6</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <f aca="false">ROUND(C16*Summary!$C$9,0)</f>
+        <v>7121432</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="27" t="n">
-        <f aca="false">C13+C14</f>
-        <v>571230</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <f aca="false">ROUND(C15*Summary!$C$9,0)</f>
-        <v>43127865</v>
-      </c>
-      <c r="E15" s="28"/>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <f aca="false">ROUND(C15*Summary!$C$8,2)</f>
-        <v>68547.6</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <f aca="false">ROUND(C16*Summary!$C$9,0)</f>
-        <v>5175344</v>
-      </c>
-      <c r="E16" s="25" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="27" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="26" t="s">
+      <c r="C17" s="28" t="n">
+        <f aca="false">C15+C16</f>
+        <v>880353.6</v>
+      </c>
+      <c r="D17" s="28" t="n">
+        <f aca="false">ROUND(C17*Summary!$C$9,0)</f>
+        <v>66466697</v>
+      </c>
+      <c r="E17" s="29"/>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="27" t="n">
-        <f aca="false">C15+C16</f>
-        <v>639777.6</v>
-      </c>
-      <c r="D17" s="27" t="n">
-        <f aca="false">ROUND(C17*Summary!$C$9,0)</f>
-        <v>48303209</v>
-      </c>
-      <c r="E17" s="28"/>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="25" t="n">
+        <f aca="false">ROUND(C17*Summary!$C$7,2)</f>
+        <v>132053.04</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <f aca="false">ROUND(C18*Summary!$C$9,0)</f>
+        <v>9970005</v>
+      </c>
+      <c r="E18" s="26"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="24" t="n">
-        <f aca="false">ROUND(C17*Summary!$C$7,2)</f>
-        <v>95966.64</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <f aca="false">ROUND(C18*Summary!$C$9,0)</f>
-        <v>7245481</v>
-      </c>
-      <c r="E18" s="25"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29" t="s">
+      <c r="C19" s="31" t="n">
+        <f aca="false">C17+C18</f>
+        <v>1012406.64</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <f aca="false">ROUND(C19*Summary!$C$9,0)</f>
+        <v>76436701</v>
+      </c>
+      <c r="E19" s="33" t="s">
         <v>38</v>
-      </c>
-      <c r="C19" s="30" t="n">
-        <f aca="false">C17+C18</f>
-        <v>735744.24</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <f aca="false">ROUND(C19*Summary!$C$9,0)</f>
-        <v>55548690</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -2259,126 +2102,134 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="D22" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="E22" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="23" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="24" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="34" t="n">
+        <f aca="false">'Lot A - Forum'!F22</f>
+        <v>524552</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <f aca="false">'Lot A - Forum'!F24</f>
+        <v>603234.8</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <f aca="false">ROUND(D23*Summary!$C$9,0)</f>
+        <v>45544227</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="33" t="n">
-        <f aca="false">'Lot A - Forum'!F19</f>
-        <v>283976</v>
-      </c>
-      <c r="D23" s="33" t="n">
-        <f aca="false">'Lot A - Forum'!F21</f>
-        <v>326572.4</v>
-      </c>
-      <c r="E23" s="24" t="n">
-        <f aca="false">ROUND(D23*Summary!$C$9,0)</f>
-        <v>24656216</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="33" t="n">
-        <f aca="false">'Lot B - Pavilion'!F18</f>
+      <c r="C24" s="34" t="n">
+        <f aca="false">'Lot B - Pavilion'!F13</f>
         <v>355801.6</v>
       </c>
-      <c r="D24" s="33" t="n">
-        <f aca="false">'Lot B - Pavilion'!F20</f>
+      <c r="D24" s="34" t="n">
+        <f aca="false">'Lot B - Pavilion'!F15</f>
         <v>409171.84</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="25" t="n">
         <f aca="false">ROUND(D24*Summary!$C$9,0)</f>
         <v>30892474</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-    </row>
-    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="34" t="s">
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="34" t="s">
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="34" t="s">
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-    </row>
-    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="34" t="s">
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-    </row>
-    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="34" t="s">
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="34" t="s">
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="34" t="s">
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B4:E4"/>
@@ -2397,6 +2248,7 @@
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>
@@ -2413,10 +2265,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
@@ -2450,517 +2302,599 @@
       <c r="H2" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
+    <row r="5" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="39" t="n">
-        <v>22500</v>
-      </c>
-      <c r="F5" s="40" t="n">
+      <c r="E5" s="40" t="n">
+        <v>325000</v>
+      </c>
+      <c r="F5" s="41" t="n">
         <f aca="false">ROUND(C5*E5,2)</f>
-        <v>22500</v>
-      </c>
-      <c r="G5" s="41" t="n">
+        <v>325000</v>
+      </c>
+      <c r="G5" s="42" t="n">
         <f aca="false">ROUND(E5*Summary!$C$9,0)</f>
-        <v>1698750</v>
-      </c>
-      <c r="H5" s="41" t="n">
+        <v>24537500</v>
+      </c>
+      <c r="H5" s="42" t="n">
         <f aca="false">ROUND(F5*Summary!$C$9,0)</f>
-        <v>1698750</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
+        <v>24537500</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="45" t="n">
+      <c r="D6" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <f aca="false">ROUND(C6*E6,2)</f>
+        <v>13000</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <f aca="false">ROUND(E6*Summary!$C$9,0)</f>
+        <v>981500</v>
+      </c>
+      <c r="H6" s="48" t="n">
+        <f aca="false">ROUND(F6*Summary!$C$9,0)</f>
+        <v>981500</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F7" s="41" t="n">
+        <f aca="false">ROUND(C7*E7,2)</f>
+        <v>9500</v>
+      </c>
+      <c r="G7" s="42" t="n">
+        <f aca="false">ROUND(E7*Summary!$C$9,0)</f>
+        <v>717250</v>
+      </c>
+      <c r="H7" s="42" t="n">
+        <f aca="false">ROUND(F7*Summary!$C$9,0)</f>
+        <v>717250</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="46" t="n">
         <v>15750</v>
       </c>
-      <c r="F6" s="46" t="n">
-        <f aca="false">ROUND(C6*E6,2)</f>
+      <c r="F8" s="47" t="n">
+        <f aca="false">ROUND(C8*E8,2)</f>
         <v>15750</v>
       </c>
-      <c r="G6" s="47" t="n">
-        <f aca="false">ROUND(E6*Summary!$C$9,0)</f>
+      <c r="G8" s="48" t="n">
+        <f aca="false">ROUND(E8*Summary!$C$9,0)</f>
         <v>1189125</v>
       </c>
-      <c r="H6" s="47" t="n">
-        <f aca="false">ROUND(F6*Summary!$C$9,0)</f>
+      <c r="H8" s="48" t="n">
+        <f aca="false">ROUND(F8*Summary!$C$9,0)</f>
         <v>1189125</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
+    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="38" t="n">
+      <c r="E9" s="40" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F9" s="41" t="n">
+        <f aca="false">ROUND(C9*E9,2)</f>
+        <v>8400</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <f aca="false">ROUND(E9*Summary!$C$9,0)</f>
+        <v>634200</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <f aca="false">ROUND(F9*Summary!$C$9,0)</f>
+        <v>634200</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>8400</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <f aca="false">ROUND(C7*E7,2)</f>
-        <v>8400</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <f aca="false">ROUND(E7*Summary!$C$9,0)</f>
-        <v>634200</v>
-      </c>
-      <c r="H7" s="41" t="n">
-        <f aca="false">ROUND(F7*Summary!$C$9,0)</f>
-        <v>634200</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="44" t="n">
+      <c r="D10" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <f aca="false">ROUND(C10*E10,2)</f>
+        <v>10800</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <f aca="false">ROUND(E10*Summary!$C$9,0)</f>
+        <v>815400</v>
+      </c>
+      <c r="H10" s="48" t="n">
+        <f aca="false">ROUND(F10*Summary!$C$9,0)</f>
+        <v>815400</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <f aca="false">ROUND(C11*E11,2)</f>
+        <v>4100</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <f aca="false">ROUND(E11*Summary!$C$9,0)</f>
+        <v>77388</v>
+      </c>
+      <c r="H11" s="42" t="n">
+        <f aca="false">ROUND(F11*Summary!$C$9,0)</f>
+        <v>309550</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="45" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F8" s="46" t="n">
-        <f aca="false">ROUND(C8*E8,2)</f>
-        <v>10800</v>
-      </c>
-      <c r="G8" s="47" t="n">
-        <f aca="false">ROUND(E8*Summary!$C$9,0)</f>
-        <v>815400</v>
-      </c>
-      <c r="H8" s="47" t="n">
-        <f aca="false">ROUND(F8*Summary!$C$9,0)</f>
-        <v>815400</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="38" t="n">
+      <c r="D12" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="46" t="n">
+        <v>19900</v>
+      </c>
+      <c r="F12" s="47" t="n">
+        <f aca="false">ROUND(C12*E12,2)</f>
+        <v>19900</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <f aca="false">ROUND(E12*Summary!$C$9,0)</f>
+        <v>1502450</v>
+      </c>
+      <c r="H12" s="48" t="n">
+        <f aca="false">ROUND(F12*Summary!$C$9,0)</f>
+        <v>1502450</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="40" t="n">
+        <v>26500</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <f aca="false">ROUND(C13*E13,2)</f>
+        <v>26500</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <f aca="false">ROUND(E13*Summary!$C$9,0)</f>
+        <v>2000750</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <f aca="false">ROUND(F13*Summary!$C$9,0)</f>
+        <v>2000750</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>1025</v>
-      </c>
-      <c r="F9" s="40" t="n">
-        <f aca="false">ROUND(C9*E9,2)</f>
-        <v>4100</v>
-      </c>
-      <c r="G9" s="41" t="n">
-        <f aca="false">ROUND(E9*Summary!$C$9,0)</f>
-        <v>77388</v>
-      </c>
-      <c r="H9" s="41" t="n">
-        <f aca="false">ROUND(F9*Summary!$C$9,0)</f>
-        <v>309550</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="44" t="n">
+      <c r="D14" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <f aca="false">ROUND(C14*E14,2)</f>
+        <v>9600</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <f aca="false">ROUND(E14*Summary!$C$9,0)</f>
+        <v>181200</v>
+      </c>
+      <c r="H14" s="48" t="n">
+        <f aca="false">ROUND(F14*Summary!$C$9,0)</f>
+        <v>724800</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="45" t="n">
-        <v>19900</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <f aca="false">ROUND(C10*E10,2)</f>
-        <v>19900</v>
-      </c>
-      <c r="G10" s="47" t="n">
-        <f aca="false">ROUND(E10*Summary!$C$9,0)</f>
-        <v>1502450</v>
-      </c>
-      <c r="H10" s="47" t="n">
-        <f aca="false">ROUND(F10*Summary!$C$9,0)</f>
-        <v>1502450</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="39" t="n">
-        <v>26500</v>
-      </c>
-      <c r="F11" s="40" t="n">
-        <f aca="false">ROUND(C11*E11,2)</f>
-        <v>26500</v>
-      </c>
-      <c r="G11" s="41" t="n">
-        <f aca="false">ROUND(E11*Summary!$C$9,0)</f>
-        <v>2000750</v>
-      </c>
-      <c r="H11" s="41" t="n">
-        <f aca="false">ROUND(F11*Summary!$C$9,0)</f>
-        <v>2000750</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="45" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <f aca="false">ROUND(C12*E12,2)</f>
-        <v>9600</v>
-      </c>
-      <c r="G12" s="47" t="n">
-        <f aca="false">ROUND(E12*Summary!$C$9,0)</f>
-        <v>181200</v>
-      </c>
-      <c r="H12" s="47" t="n">
-        <f aca="false">ROUND(F12*Summary!$C$9,0)</f>
-        <v>724800</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="39" t="n">
+      <c r="D15" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="40" t="n">
         <v>4500</v>
       </c>
-      <c r="F13" s="40" t="n">
-        <f aca="false">ROUND(C13*E13,2)</f>
-        <v>4500</v>
-      </c>
-      <c r="G13" s="41" t="n">
-        <f aca="false">ROUND(E13*Summary!$C$9,0)</f>
-        <v>339750</v>
-      </c>
-      <c r="H13" s="41" t="n">
-        <f aca="false">ROUND(F13*Summary!$C$9,0)</f>
-        <v>339750</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="44" t="n">
-        <v>300</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="45" t="n">
-        <v>395</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <f aca="false">ROUND(C14*E14,2)</f>
-        <v>118500</v>
-      </c>
-      <c r="G14" s="47" t="n">
-        <f aca="false">ROUND(E14*Summary!$C$9,0)</f>
-        <v>29823</v>
-      </c>
-      <c r="H14" s="47" t="n">
-        <f aca="false">ROUND(F14*Summary!$C$9,0)</f>
-        <v>8946750</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="41" t="n">
         <f aca="false">ROUND(C15*E15,2)</f>
         <v>4500</v>
       </c>
-      <c r="G15" s="41" t="n">
+      <c r="G15" s="42" t="n">
         <f aca="false">ROUND(E15*Summary!$C$9,0)</f>
         <v>339750</v>
       </c>
-      <c r="H15" s="41" t="n">
+      <c r="H15" s="42" t="n">
         <f aca="false">ROUND(F15*Summary!$C$9,0)</f>
         <v>339750</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="42" t="s">
+    <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C16" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="45" t="n">
+      <c r="D17" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <f aca="false">ROUND(C17*E17,2)</f>
+        <v>4500</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <f aca="false">ROUND(E17*Summary!$C$9,0)</f>
+        <v>339750</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <f aca="false">ROUND(F17*Summary!$C$9,0)</f>
+        <v>339750</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="46" t="n">
         <v>8500</v>
       </c>
-      <c r="F16" s="46" t="n">
-        <f aca="false">ROUND(C16*E16,2)</f>
+      <c r="F18" s="47" t="n">
+        <f aca="false">ROUND(C18*E18,2)</f>
         <v>8500</v>
       </c>
-      <c r="G16" s="47" t="n">
-        <f aca="false">ROUND(E16*Summary!$C$9,0)</f>
+      <c r="G18" s="48" t="n">
+        <f aca="false">ROUND(E18*Summary!$C$9,0)</f>
         <v>641750</v>
       </c>
-      <c r="H16" s="47" t="n">
-        <f aca="false">ROUND(F16*Summary!$C$9,0)</f>
+      <c r="H18" s="48" t="n">
+        <f aca="false">ROUND(F18*Summary!$C$9,0)</f>
         <v>641750</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="49" t="n">
-        <f aca="false">SUM(F5:F16)</f>
-        <v>253550</v>
-      </c>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51" t="n">
-        <f aca="false">ROUND(F17*Summary!$C$9,0)</f>
-        <v>19143025</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="52"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="53" t="n">
-        <f aca="false">ROUND(F17*Summary!$C$8,2)</f>
-        <v>30426</v>
-      </c>
-      <c r="G18" s="54"/>
-      <c r="H18" s="41" t="n">
-        <f aca="false">ROUND(F18*Summary!$C$9,0)</f>
-        <v>2297163</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="49" t="n">
-        <f aca="false">F17+F18</f>
-        <v>283976</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51" t="n">
+    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>830</v>
+      </c>
+      <c r="F19" s="41" t="n">
+        <f aca="false">ROUND(C19*E19,2)</f>
+        <v>8300</v>
+      </c>
+      <c r="G19" s="42" t="n">
+        <f aca="false">ROUND(E19*Summary!$C$9,0)</f>
+        <v>62665</v>
+      </c>
+      <c r="H19" s="42" t="n">
         <f aca="false">ROUND(F19*Summary!$C$9,0)</f>
-        <v>21440188</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>626650</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="52" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B20" s="52"/>
       <c r="C20" s="52"/>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
       <c r="F20" s="53" t="n">
-        <f aca="false">ROUND(F19*Summary!$C$7,2)</f>
-        <v>42596.4</v>
+        <f aca="false">SUM(F5:F19)</f>
+        <v>468350</v>
       </c>
       <c r="G20" s="54"/>
-      <c r="H20" s="41" t="n">
+      <c r="H20" s="55" t="n">
         <f aca="false">ROUND(F20*Summary!$C$9,0)</f>
-        <v>3216028</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="55" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="56" t="n">
-        <f aca="false">F19+F20</f>
-        <v>326572.4</v>
-      </c>
-      <c r="G21" s="57"/>
-      <c r="H21" s="58" t="n">
+        <v>35360425</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="57" t="n">
+        <f aca="false">ROUND(F20*Summary!$C$8,2)</f>
+        <v>56202</v>
+      </c>
+      <c r="G21" s="58"/>
+      <c r="H21" s="42" t="n">
         <f aca="false">ROUND(F21*Summary!$C$9,0)</f>
-        <v>24656216</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-    </row>
-    <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>4243251</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="53" t="n">
+        <f aca="false">F20+F21</f>
+        <v>524552</v>
+      </c>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55" t="n">
+        <f aca="false">ROUND(F22*Summary!$C$9,0)</f>
+        <v>39603676</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="57" t="n">
+        <f aca="false">ROUND(F22*Summary!$C$7,2)</f>
+        <v>78682.8</v>
+      </c>
+      <c r="G23" s="58"/>
+      <c r="H23" s="42" t="n">
+        <f aca="false">ROUND(F23*Summary!$C$9,0)</f>
+        <v>5940551</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B24" s="59"/>
       <c r="C24" s="59"/>
       <c r="D24" s="59"/>
       <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
+      <c r="F24" s="31" t="n">
+        <f aca="false">F22+F23</f>
+        <v>603234.8</v>
+      </c>
+      <c r="G24" s="60"/>
+      <c r="H24" s="61" t="n">
+        <f aca="false">ROUND(F24*Summary!$C$9,0)</f>
+        <v>45544227</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A29:H29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>
@@ -2977,10 +2911,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
@@ -2991,7 +2925,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3003,7 +2937,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3014,488 +2948,343 @@
       <c r="H2" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
+    <row r="5" customFormat="false" ht="343.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="40" t="n">
+        <v>232000</v>
+      </c>
+      <c r="F5" s="41" t="n">
+        <f aca="false">ROUND(C5*E5,2)</f>
+        <v>232000</v>
+      </c>
+      <c r="G5" s="42" t="n">
+        <f aca="false">ROUND(E5*Summary!$C$9,0)</f>
+        <v>17516000</v>
+      </c>
+      <c r="H5" s="42" t="n">
+        <f aca="false">ROUND(F5*Summary!$C$9,0)</f>
+        <v>17516000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>4250</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <f aca="false">ROUND(C6*E6,2)</f>
+        <v>17000</v>
+      </c>
+      <c r="G6" s="48" t="n">
+        <f aca="false">ROUND(E6*Summary!$C$9,0)</f>
+        <v>320875</v>
+      </c>
+      <c r="H6" s="48" t="n">
+        <f aca="false">ROUND(F6*Summary!$C$9,0)</f>
+        <v>1283500</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="40" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F7" s="41" t="n">
+        <f aca="false">ROUND(C7*E7,2)</f>
+        <v>19200</v>
+      </c>
+      <c r="G7" s="42" t="n">
+        <f aca="false">ROUND(E7*Summary!$C$9,0)</f>
+        <v>362400</v>
+      </c>
+      <c r="H7" s="42" t="n">
+        <f aca="false">ROUND(F7*Summary!$C$9,0)</f>
+        <v>1449600</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>880</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <f aca="false">ROUND(C8*E8,2)</f>
+        <v>3080</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <f aca="false">ROUND(E8*Summary!$C$9,0)</f>
+        <v>264</v>
+      </c>
+      <c r="H8" s="48" t="n">
+        <f aca="false">ROUND(F8*Summary!$C$9,0)</f>
+        <v>232540</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F9" s="41" t="n">
+        <f aca="false">ROUND(C9*E9,2)</f>
+        <v>7400</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <f aca="false">ROUND(E9*Summary!$C$9,0)</f>
+        <v>139675</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <f aca="false">ROUND(F9*Summary!$C$9,0)</f>
+        <v>558700</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>9750</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <f aca="false">ROUND(C10*E10,2)</f>
+        <v>39000</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <f aca="false">ROUND(E10*Summary!$C$9,0)</f>
+        <v>736125</v>
+      </c>
+      <c r="H10" s="48" t="n">
+        <f aca="false">ROUND(F10*Summary!$C$9,0)</f>
+        <v>2944500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53" t="n">
+        <f aca="false">SUM(F5:F10)</f>
+        <v>317680</v>
+      </c>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55" t="n">
+        <f aca="false">ROUND(F11*Summary!$C$9,0)</f>
+        <v>23984840</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="39" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F5" s="40" t="n">
-        <f aca="false">ROUND(C5*E5,2)</f>
-        <v>58000</v>
-      </c>
-      <c r="G5" s="41" t="n">
-        <f aca="false">ROUND(E5*Summary!$C$9,0)</f>
-        <v>4379000</v>
-      </c>
-      <c r="H5" s="41" t="n">
-        <f aca="false">ROUND(F5*Summary!$C$9,0)</f>
-        <v>4379000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="42" t="s">
+      <c r="B12" s="56"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="57" t="n">
+        <f aca="false">ROUND(F11*Summary!$C$8,2)</f>
+        <v>38121.6</v>
+      </c>
+      <c r="G12" s="58"/>
+      <c r="H12" s="42" t="n">
+        <f aca="false">ROUND(F12*Summary!$C$9,0)</f>
+        <v>2878181</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="53" t="n">
+        <f aca="false">F11+F12</f>
+        <v>355801.6</v>
+      </c>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55" t="n">
+        <f aca="false">ROUND(F13*Summary!$C$9,0)</f>
+        <v>26863021</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="45" t="n">
-        <v>96000</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <f aca="false">ROUND(C6*E6,2)</f>
-        <v>96000</v>
-      </c>
-      <c r="G6" s="47" t="n">
-        <f aca="false">ROUND(E6*Summary!$C$9,0)</f>
-        <v>7248000</v>
-      </c>
-      <c r="H6" s="47" t="n">
-        <f aca="false">ROUND(F6*Summary!$C$9,0)</f>
-        <v>7248000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <f aca="false">ROUND(C7*E7,2)</f>
-        <v>40000</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <f aca="false">ROUND(E7*Summary!$C$9,0)</f>
-        <v>3020000</v>
-      </c>
-      <c r="H7" s="41" t="n">
-        <f aca="false">ROUND(F7*Summary!$C$9,0)</f>
-        <v>3020000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="45" t="n">
-        <v>12500</v>
-      </c>
-      <c r="F8" s="46" t="n">
-        <f aca="false">ROUND(C8*E8,2)</f>
-        <v>12500</v>
-      </c>
-      <c r="G8" s="47" t="n">
-        <f aca="false">ROUND(E8*Summary!$C$9,0)</f>
-        <v>943750</v>
-      </c>
-      <c r="H8" s="47" t="n">
-        <f aca="false">ROUND(F8*Summary!$C$9,0)</f>
-        <v>943750</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="39" t="n">
-        <v>16500</v>
-      </c>
-      <c r="F9" s="40" t="n">
-        <f aca="false">ROUND(C9*E9,2)</f>
-        <v>16500</v>
-      </c>
-      <c r="G9" s="41" t="n">
-        <f aca="false">ROUND(E9*Summary!$C$9,0)</f>
-        <v>1245750</v>
-      </c>
-      <c r="H9" s="41" t="n">
-        <f aca="false">ROUND(F9*Summary!$C$9,0)</f>
-        <v>1245750</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="45" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <f aca="false">ROUND(C10*E10,2)</f>
-        <v>9000</v>
-      </c>
-      <c r="G10" s="47" t="n">
-        <f aca="false">ROUND(E10*Summary!$C$9,0)</f>
-        <v>679500</v>
-      </c>
-      <c r="H10" s="47" t="n">
-        <f aca="false">ROUND(F10*Summary!$C$9,0)</f>
-        <v>679500</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="39" t="n">
-        <v>4250</v>
-      </c>
-      <c r="F11" s="40" t="n">
-        <f aca="false">ROUND(C11*E11,2)</f>
-        <v>17000</v>
-      </c>
-      <c r="G11" s="41" t="n">
-        <f aca="false">ROUND(E11*Summary!$C$9,0)</f>
-        <v>320875</v>
-      </c>
-      <c r="H11" s="41" t="n">
-        <f aca="false">ROUND(F11*Summary!$C$9,0)</f>
-        <v>1283500</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="45" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <f aca="false">ROUND(C12*E12,2)</f>
-        <v>19200</v>
-      </c>
-      <c r="G12" s="47" t="n">
-        <f aca="false">ROUND(E12*Summary!$C$9,0)</f>
-        <v>362400</v>
-      </c>
-      <c r="H12" s="47" t="n">
-        <f aca="false">ROUND(F12*Summary!$C$9,0)</f>
-        <v>1449600</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="38" t="n">
-        <v>880</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="60" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F13" s="40" t="n">
-        <f aca="false">ROUND(C13*E13,2)</f>
-        <v>3080</v>
-      </c>
-      <c r="G13" s="41" t="n">
-        <f aca="false">ROUND(E13*Summary!$C$9,0)</f>
-        <v>264</v>
-      </c>
-      <c r="H13" s="41" t="n">
-        <f aca="false">ROUND(F13*Summary!$C$9,0)</f>
-        <v>232540</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="44" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="45" t="n">
-        <v>1850</v>
-      </c>
-      <c r="F14" s="46" t="n">
-        <f aca="false">ROUND(C14*E14,2)</f>
-        <v>7400</v>
-      </c>
-      <c r="G14" s="47" t="n">
-        <f aca="false">ROUND(E14*Summary!$C$9,0)</f>
-        <v>139675</v>
-      </c>
-      <c r="H14" s="47" t="n">
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="57" t="n">
+        <f aca="false">ROUND(F13*Summary!$C$7,2)</f>
+        <v>53370.24</v>
+      </c>
+      <c r="G14" s="58"/>
+      <c r="H14" s="42" t="n">
         <f aca="false">ROUND(F14*Summary!$C$9,0)</f>
-        <v>558700</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="37" t="s">
+        <v>4029453</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>9750</v>
-      </c>
-      <c r="F15" s="40" t="n">
-        <f aca="false">ROUND(C15*E15,2)</f>
-        <v>39000</v>
-      </c>
-      <c r="G15" s="41" t="n">
-        <f aca="false">ROUND(E15*Summary!$C$9,0)</f>
-        <v>736125</v>
-      </c>
-      <c r="H15" s="41" t="n">
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="31" t="n">
+        <f aca="false">F13+F14</f>
+        <v>409171.84</v>
+      </c>
+      <c r="G15" s="60"/>
+      <c r="H15" s="61" t="n">
         <f aca="false">ROUND(F15*Summary!$C$9,0)</f>
-        <v>2944500</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="49" t="n">
-        <f aca="false">SUM(F5:F15)</f>
-        <v>317680</v>
-      </c>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51" t="n">
-        <f aca="false">ROUND(F16*Summary!$C$9,0)</f>
-        <v>23984840</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53" t="n">
-        <f aca="false">ROUND(F16*Summary!$C$8,2)</f>
-        <v>38121.6</v>
-      </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="41" t="n">
-        <f aca="false">ROUND(F17*Summary!$C$9,0)</f>
-        <v>2878181</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="49" t="n">
-        <f aca="false">F16+F17</f>
-        <v>355801.6</v>
-      </c>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51" t="n">
-        <f aca="false">ROUND(F18*Summary!$C$9,0)</f>
-        <v>26863021</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="52"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="53" t="n">
-        <f aca="false">ROUND(F18*Summary!$C$7,2)</f>
-        <v>53370.24</v>
-      </c>
-      <c r="G19" s="54"/>
-      <c r="H19" s="41" t="n">
-        <f aca="false">ROUND(F19*Summary!$C$9,0)</f>
-        <v>4029453</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="55" t="s">
+        <v>30892474</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="56" t="n">
-        <f aca="false">F18+F19</f>
-        <v>409171.84</v>
-      </c>
-      <c r="G20" s="57"/>
-      <c r="H20" s="58" t="n">
-        <f aca="false">ROUND(F20*Summary!$C$9,0)</f>
-        <v>30892474</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="59" t="s">
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+    </row>
+    <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-    </row>
-    <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="59" t="s">
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>
@@ -3512,231 +3301,172 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="23" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="B5" s="38" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="61" t="s">
+      <c r="C5" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="38" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="B6" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="C6" s="67" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B7" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C7" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="64" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="66" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="61" t="s">
+      <c r="B8" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C8" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="37" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="B9" s="38" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
+      <c r="C9" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="44" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="B10" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="C10" s="67" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="61" t="s">
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B11" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C11" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="62" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="66" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
+      <c r="B12" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="C12" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="43" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="D10" s="64" t="s">
+      <c r="B13" s="38" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="61" t="s">
+      <c r="C13" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="38" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="B14" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="C14" s="67" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="64" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
+      <c r="B15" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="C15" s="65" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="68" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="61" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="62" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="D15" s="62" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>179</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="64" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="62" t="s">
-        <v>186</v>
-      </c>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>
@@ -3753,189 +3483,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>195</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="61" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="66" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="61" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="66" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>212</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>218</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A17:C17"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;8 &amp;K5b6b6eMiradore Experiences — Riyadh, KSA   |   Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -3948,7 +3496,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3959,7 +3507,7 @@
     </row>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3970,543 +3518,595 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>229</v>
+        <v>172</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="68" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="69" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="70" t="n">
+      <c r="B5" s="70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F5</f>
-        <v>22500</v>
-      </c>
-      <c r="D5" s="71" t="n">
-        <v>17400</v>
-      </c>
-      <c r="E5" s="70" t="n">
+        <v>325000</v>
+      </c>
+      <c r="D5" s="72" t="n">
+        <v>325000</v>
+      </c>
+      <c r="E5" s="71" t="n">
         <f aca="false">C5-D5</f>
-        <v>5100</v>
-      </c>
-      <c r="F5" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="73" t="n">
         <f aca="false">IF(D5=0,"n/a",C5/D5-1)</f>
-        <v>0.293103448275862</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>233</v>
+        <v>0</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="C6" s="70" t="n">
+      <c r="B6" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F6</f>
+        <v>13000</v>
+      </c>
+      <c r="D6" s="72" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E6" s="71" t="n">
+        <f aca="false">C6-D6</f>
+        <v>3000</v>
+      </c>
+      <c r="F6" s="73" t="n">
+        <f aca="false">IF(D6=0,"n/a",C6/D6-1)</f>
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="70" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F7</f>
+        <v>9500</v>
+      </c>
+      <c r="D7" s="72" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E7" s="71" t="n">
+        <f aca="false">C7-D7</f>
+        <v>2100</v>
+      </c>
+      <c r="F7" s="73" t="n">
+        <f aca="false">IF(D7=0,"n/a",C7/D7-1)</f>
+        <v>0.283783783783784</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F8</f>
         <v>15750</v>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D8" s="72" t="n">
         <v>12250</v>
       </c>
-      <c r="E6" s="70" t="n">
-        <f aca="false">C6-D6</f>
+      <c r="E8" s="71" t="n">
+        <f aca="false">C8-D8</f>
         <v>3500</v>
       </c>
-      <c r="F6" s="72" t="n">
-        <f aca="false">IF(D6=0,"n/a",C6/D6-1)</f>
+      <c r="F8" s="73" t="n">
+        <f aca="false">IF(D8=0,"n/a",C8/D8-1)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="G6" s="25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="68" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="69" t="s">
-        <v>236</v>
-      </c>
-      <c r="C7" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F7</f>
+      <c r="G8" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="70" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F9</f>
         <v>8400</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D9" s="72" t="n">
         <v>6500</v>
       </c>
-      <c r="E7" s="70" t="n">
-        <f aca="false">C7-D7</f>
+      <c r="E9" s="71" t="n">
+        <f aca="false">C9-D9</f>
         <v>1900</v>
       </c>
-      <c r="F7" s="72" t="n">
-        <f aca="false">IF(D7=0,"n/a",C7/D7-1)</f>
+      <c r="F9" s="73" t="n">
+        <f aca="false">IF(D9=0,"n/a",C9/D9-1)</f>
         <v>0.292307692307692</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="68" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="69" t="s">
-        <v>238</v>
-      </c>
-      <c r="C8" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F8</f>
+      <c r="G9" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="70" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F10</f>
         <v>10800</v>
       </c>
-      <c r="D8" s="71" t="n">
+      <c r="D10" s="72" t="n">
         <v>8500</v>
       </c>
-      <c r="E8" s="70" t="n">
-        <f aca="false">C8-D8</f>
+      <c r="E10" s="71" t="n">
+        <f aca="false">C10-D10</f>
         <v>2300</v>
       </c>
-      <c r="F8" s="72" t="n">
-        <f aca="false">IF(D8=0,"n/a",C8/D8-1)</f>
+      <c r="F10" s="73" t="n">
+        <f aca="false">IF(D10=0,"n/a",C10/D10-1)</f>
         <v>0.270588235294118</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F9</f>
+      <c r="G10" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F11</f>
         <v>4100</v>
       </c>
-      <c r="D9" s="71" t="n">
+      <c r="D11" s="72" t="n">
         <v>3200</v>
       </c>
-      <c r="E9" s="70" t="n">
-        <f aca="false">C9-D9</f>
+      <c r="E11" s="71" t="n">
+        <f aca="false">C11-D11</f>
         <v>900</v>
       </c>
-      <c r="F9" s="72" t="n">
-        <f aca="false">IF(D9=0,"n/a",C9/D9-1)</f>
+      <c r="F11" s="73" t="n">
+        <f aca="false">IF(D11=0,"n/a",C11/D11-1)</f>
         <v>0.28125</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F10</f>
+      <c r="G11" s="26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="70" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F12</f>
         <v>19900</v>
       </c>
-      <c r="D10" s="71" t="n">
+      <c r="D12" s="72" t="n">
         <v>15500</v>
       </c>
-      <c r="E10" s="70" t="n">
-        <f aca="false">C10-D10</f>
+      <c r="E12" s="71" t="n">
+        <f aca="false">C12-D12</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="72" t="n">
-        <f aca="false">IF(D10=0,"n/a",C10/D10-1)</f>
+      <c r="F12" s="73" t="n">
+        <f aca="false">IF(D12=0,"n/a",C12/D12-1)</f>
         <v>0.283870967741936</v>
       </c>
-      <c r="G10" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="68" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F11</f>
+      <c r="G12" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F13</f>
         <v>26500</v>
       </c>
-      <c r="D11" s="71" t="n">
+      <c r="D13" s="72" t="n">
         <v>20500</v>
       </c>
-      <c r="E11" s="70" t="n">
-        <f aca="false">C11-D11</f>
+      <c r="E13" s="71" t="n">
+        <f aca="false">C13-D13</f>
         <v>6000</v>
       </c>
-      <c r="F11" s="72" t="n">
-        <f aca="false">IF(D11=0,"n/a",C11/D11-1)</f>
+      <c r="F13" s="73" t="n">
+        <f aca="false">IF(D13=0,"n/a",C13/D13-1)</f>
         <v>0.292682926829268</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F12</f>
+      <c r="G13" s="26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F14</f>
         <v>9600</v>
       </c>
-      <c r="D12" s="71" t="n">
+      <c r="D14" s="72" t="n">
         <v>6300</v>
       </c>
-      <c r="E12" s="70" t="n">
-        <f aca="false">C12-D12</f>
+      <c r="E14" s="71" t="n">
+        <f aca="false">C14-D14</f>
         <v>3300</v>
       </c>
-      <c r="F12" s="72" t="n">
-        <f aca="false">IF(D12=0,"n/a",C12/D12-1)</f>
+      <c r="F14" s="73" t="n">
+        <f aca="false">IF(D14=0,"n/a",C14/D14-1)</f>
         <v>0.523809523809524</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="68" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F13</f>
-        <v>4500</v>
-      </c>
-      <c r="D13" s="71" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E13" s="70" t="n">
-        <f aca="false">C13-D13</f>
-        <v>1700</v>
-      </c>
-      <c r="F13" s="72" t="n">
-        <f aca="false">IF(D13=0,"n/a",C13/D13-1)</f>
-        <v>0.607142857142857</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="C14" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F14</f>
-        <v>118500</v>
-      </c>
-      <c r="D14" s="71" t="n">
-        <v>97500</v>
-      </c>
-      <c r="E14" s="70" t="n">
-        <f aca="false">C14-D14</f>
-        <v>21000</v>
-      </c>
-      <c r="F14" s="72" t="n">
-        <f aca="false">IF(D14=0,"n/a",C14/D14-1)</f>
-        <v>0.215384615384615</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>251</v>
+      <c r="G14" s="26" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="69" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="70" t="n">
+      <c r="B15" s="70" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F15</f>
         <v>4500</v>
       </c>
-      <c r="D15" s="71" t="n">
+      <c r="D15" s="72" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E15" s="71" t="n">
+        <f aca="false">C15-D15</f>
+        <v>1700</v>
+      </c>
+      <c r="F15" s="73" t="n">
+        <f aca="false">IF(D15=0,"n/a",C15/D15-1)</f>
+        <v>0.607142857142857</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="70" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F17</f>
+        <v>4500</v>
+      </c>
+      <c r="D16" s="72" t="n">
         <v>2500</v>
       </c>
-      <c r="E15" s="70" t="n">
-        <f aca="false">C15-D15</f>
+      <c r="E16" s="71" t="n">
+        <f aca="false">C16-D16</f>
         <v>2000</v>
       </c>
-      <c r="F15" s="72" t="n">
-        <f aca="false">IF(D15=0,"n/a",C15/D15-1)</f>
+      <c r="F16" s="73" t="n">
+        <f aca="false">IF(D16=0,"n/a",C16/D16-1)</f>
         <v>0.8</v>
       </c>
-      <c r="G15" s="25" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="69" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="70" t="n">
-        <f aca="false">'Lot A - Forum'!F16</f>
+      <c r="G16" s="26" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F18</f>
         <v>8500</v>
       </c>
-      <c r="D16" s="71" t="n">
+      <c r="D17" s="72" t="n">
         <v>6000</v>
       </c>
-      <c r="E16" s="70" t="n">
-        <f aca="false">C16-D16</f>
+      <c r="E17" s="71" t="n">
+        <f aca="false">C17-D17</f>
         <v>2500</v>
       </c>
-      <c r="F16" s="72" t="n">
-        <f aca="false">IF(D16=0,"n/a",C16/D16-1)</f>
+      <c r="F17" s="73" t="n">
+        <f aca="false">IF(D17=0,"n/a",C17/D17-1)</f>
         <v>0.416666666666667</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" s="69" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="70" t="n">
-        <f aca="false">SUM('Lot B - Pavilion'!F5:F10)</f>
+      <c r="G17" s="26" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="71" t="n">
+        <f aca="false">'Lot A - Forum'!F19</f>
+        <v>8300</v>
+      </c>
+      <c r="D18" s="72" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E18" s="71" t="n">
+        <f aca="false">C18-D18</f>
+        <v>1800</v>
+      </c>
+      <c r="F18" s="73" t="n">
+        <f aca="false">IF(D18=0,"n/a",C18/D18-1)</f>
+        <v>0.276923076923077</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F5</f>
         <v>232000</v>
       </c>
-      <c r="D17" s="71" t="n">
+      <c r="D19" s="72" t="n">
         <v>130435</v>
       </c>
-      <c r="E17" s="70" t="n">
-        <f aca="false">C17-D17</f>
+      <c r="E19" s="71" t="n">
+        <f aca="false">C19-D19</f>
         <v>101565</v>
       </c>
-      <c r="F17" s="72" t="n">
-        <f aca="false">IF(D17=0,"n/a",C17/D17-1)</f>
+      <c r="F19" s="73" t="n">
+        <f aca="false">IF(D19=0,"n/a",C19/D19-1)</f>
         <v>0.778663702227163</v>
       </c>
-      <c r="G17" s="25" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="C18" s="70" t="n">
-        <f aca="false">'Lot B - Pavilion'!F11</f>
+      <c r="G19" s="26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F6</f>
         <v>17000</v>
       </c>
-      <c r="D18" s="71" t="n">
+      <c r="D20" s="72" t="n">
         <v>6000</v>
       </c>
-      <c r="E18" s="70" t="n">
-        <f aca="false">C18-D18</f>
+      <c r="E20" s="71" t="n">
+        <f aca="false">C20-D20</f>
         <v>11000</v>
       </c>
-      <c r="F18" s="72" t="n">
-        <f aca="false">IF(D18=0,"n/a",C18/D18-1)</f>
+      <c r="F20" s="73" t="n">
+        <f aca="false">IF(D20=0,"n/a",C20/D20-1)</f>
         <v>1.83333333333333</v>
       </c>
-      <c r="G18" s="25" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="68" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>261</v>
-      </c>
-      <c r="C19" s="70" t="n">
-        <f aca="false">'Lot B - Pavilion'!F12</f>
+      <c r="G20" s="26" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="70" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F7</f>
         <v>19200</v>
       </c>
-      <c r="D19" s="71" t="n">
+      <c r="D21" s="72" t="n">
         <v>10000</v>
       </c>
-      <c r="E19" s="70" t="n">
-        <f aca="false">C19-D19</f>
+      <c r="E21" s="71" t="n">
+        <f aca="false">C21-D21</f>
         <v>9200</v>
       </c>
-      <c r="F19" s="72" t="n">
-        <f aca="false">IF(D19=0,"n/a",C19/D19-1)</f>
+      <c r="F21" s="73" t="n">
+        <f aca="false">IF(D21=0,"n/a",C21/D21-1)</f>
         <v>0.92</v>
       </c>
-      <c r="G19" s="25" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="70" t="n">
-        <f aca="false">'Lot B - Pavilion'!F13</f>
+      <c r="G21" s="26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="69" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F8</f>
         <v>3080</v>
       </c>
-      <c r="D20" s="71" t="n">
+      <c r="D22" s="72" t="n">
         <v>1320</v>
       </c>
-      <c r="E20" s="70" t="n">
-        <f aca="false">C20-D20</f>
+      <c r="E22" s="71" t="n">
+        <f aca="false">C22-D22</f>
         <v>1760</v>
       </c>
-      <c r="F20" s="72" t="n">
-        <f aca="false">IF(D20=0,"n/a",C20/D20-1)</f>
+      <c r="F22" s="73" t="n">
+        <f aca="false">IF(D22=0,"n/a",C22/D22-1)</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="G20" s="25" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="68" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="69" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21" s="70" t="n">
-        <f aca="false">'Lot B - Pavilion'!F14</f>
+      <c r="G22" s="26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F9</f>
         <v>7400</v>
       </c>
-      <c r="D21" s="71" t="n">
+      <c r="D23" s="72" t="n">
         <v>4800</v>
       </c>
-      <c r="E21" s="70" t="n">
-        <f aca="false">C21-D21</f>
+      <c r="E23" s="71" t="n">
+        <f aca="false">C23-D23</f>
         <v>2600</v>
       </c>
-      <c r="F21" s="72" t="n">
-        <f aca="false">IF(D21=0,"n/a",C21/D21-1)</f>
+      <c r="F23" s="73" t="n">
+        <f aca="false">IF(D23=0,"n/a",C23/D23-1)</f>
         <v>0.541666666666667</v>
       </c>
-      <c r="G21" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="68" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="C22" s="70" t="n">
-        <f aca="false">'Lot B - Pavilion'!F15</f>
+      <c r="G23" s="26" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="71" t="n">
+        <f aca="false">'Lot B - Pavilion'!F10</f>
         <v>39000</v>
       </c>
-      <c r="D22" s="71" t="n">
+      <c r="D24" s="72" t="n">
         <v>24000</v>
       </c>
-      <c r="E22" s="70" t="n">
-        <f aca="false">C22-D22</f>
+      <c r="E24" s="71" t="n">
+        <f aca="false">C24-D24</f>
         <v>15000</v>
       </c>
-      <c r="F22" s="72" t="n">
-        <f aca="false">IF(D22=0,"n/a",C22/D22-1)</f>
+      <c r="F24" s="73" t="n">
+        <f aca="false">IF(D24=0,"n/a",C24/D24-1)</f>
         <v>0.625</v>
       </c>
-      <c r="G22" s="25" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50"/>
-      <c r="B23" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C23" s="73" t="n">
-        <f aca="false">SUM(C5:C22)</f>
-        <v>571230</v>
-      </c>
-      <c r="D23" s="73" t="n">
-        <f aca="false">SUM(D5:D22)</f>
-        <v>375505</v>
-      </c>
-      <c r="E23" s="73" t="n">
-        <f aca="false">C23-D23</f>
-        <v>195725</v>
-      </c>
-      <c r="F23" s="74" t="n">
-        <f aca="false">IF(D23=0,"n/a",C23/D23-1)</f>
-        <v>0.521231408370062</v>
-      </c>
-      <c r="G23" s="50"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="75" t="s">
-        <v>270</v>
-      </c>
-      <c r="C24" s="76" t="n">
-        <f aca="false">ROUND(C23*Summary!$C$8,0)</f>
-        <v>68548</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="59" t="s">
-        <v>271</v>
-      </c>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
+      <c r="G24" s="26" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="54"/>
+      <c r="B25" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="75" t="n">
+        <f aca="false">SUM(C5:C24)</f>
+        <v>786030</v>
+      </c>
+      <c r="D25" s="75" t="n">
+        <f aca="false">SUM(D5:D24)</f>
+        <v>609505</v>
+      </c>
+      <c r="E25" s="75" t="n">
+        <f aca="false">C25-D25</f>
+        <v>176525</v>
+      </c>
+      <c r="F25" s="76" t="n">
+        <f aca="false">IF(D25=0,"n/a",C25/D25-1)</f>
+        <v>0.289620265625385</v>
+      </c>
+      <c r="G25" s="54"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="78" t="n">
+        <f aca="false">'Lot A - Forum'!F21+'Lot B - Pavilion'!F12</f>
+        <v>94323.6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.55" header="0.511811023622047" footer="0.5"/>

--- a/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
+++ b/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
@@ -180,7 +180,7 @@
     <t xml:space="preserve">PAYMENT TERMS &amp; KEY CONDITIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Payment strictly on actual basis post-event, upon successful delivery, verification and performance certification by PSEB (no advance payment), as per the RFP.</t>
+    <t xml:space="preserve">•  Payment Terms: 50% advance upon confirmation / work order; 30% two (2) days before the event; 20% balance after the event, upon successful delivery and verification.</t>
   </si>
   <si>
     <t xml:space="preserve">•  The Crowne Plaza Riyadh RDC venue &amp; catering package (Lot A, item A.1) is passed through at actual hotel package cost, with no markup.</t>

--- a/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
+++ b/leap2026/PSEB_LEAP2026_Commercial_Proposal_Miradore.xlsx
@@ -180,7 +180,7 @@
     <t xml:space="preserve">PAYMENT TERMS &amp; KEY CONDITIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Payment Terms: 50% advance upon confirmation / work order; 30% two (2) days before the event; 20% balance after the event, upon successful delivery and verification.</t>
+    <t xml:space="preserve">•  Preferred Payment Terms (negotiable): 50% advance upon confirmation / work order — primarily to cover the mandatory advance payment required by Crowne Plaza Riyadh RDC to secure the venue, plus mobilization of fabrication and long-lead items; 30% two (2) days before the event; 20% balance after the event, upon successful delivery and verification.</t>
   </si>
   <si>
     <t xml:space="preserve">•  The Crowne Plaza Riyadh RDC venue &amp; catering package (Lot A, item A.1) is passed through at actual hotel package cost, with no markup.</t>
@@ -1992,11 +1992,11 @@
       </c>
       <c r="C13" s="25" t="n">
         <f aca="false">'Lot A - Forum'!F20</f>
-        <v>468350</v>
+        <v>510000</v>
       </c>
       <c r="D13" s="25" t="n">
         <f aca="false">ROUND(C13*Summary!$C$9,0)</f>
-        <v>35360425</v>
+        <v>38505000</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>30</v>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="C15" s="28" t="n">
         <f aca="false">C13+C14</f>
-        <v>786030</v>
+        <v>827680</v>
       </c>
       <c r="D15" s="28" t="n">
         <f aca="false">ROUND(C15*Summary!$C$9,0)</f>
-        <v>59345265</v>
+        <v>62489840</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -2038,11 +2038,11 @@
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">'Lot A - Forum'!F21+'Lot B - Pavilion'!F12</f>
-        <v>94323.6</v>
+        <v>99321.6</v>
       </c>
       <c r="D16" s="25" t="n">
         <f aca="false">ROUND(C16*Summary!$C$9,0)</f>
-        <v>7121432</v>
+        <v>7498781</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>34</v>
@@ -2054,11 +2054,11 @@
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">C15+C16</f>
-        <v>880353.6</v>
+        <v>927001.6</v>
       </c>
       <c r="D17" s="28" t="n">
         <f aca="false">ROUND(C17*Summary!$C$9,0)</f>
-        <v>66466697</v>
+        <v>69988621</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="C18" s="25" t="n">
         <f aca="false">ROUND(C17*Summary!$C$7,2)</f>
-        <v>132053.04</v>
+        <v>139050.24</v>
       </c>
       <c r="D18" s="25" t="n">
         <f aca="false">ROUND(C18*Summary!$C$9,0)</f>
-        <v>9970005</v>
+        <v>10498293</v>
       </c>
       <c r="E18" s="26"/>
     </row>
@@ -2082,11 +2082,11 @@
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">C17+C18</f>
-        <v>1012406.64</v>
+        <v>1066051.84</v>
       </c>
       <c r="D19" s="32" t="n">
         <f aca="false">ROUND(C19*Summary!$C$9,0)</f>
-        <v>76436701</v>
+        <v>80486914</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>38</v>
@@ -2120,15 +2120,15 @@
       </c>
       <c r="C23" s="34" t="n">
         <f aca="false">'Lot A - Forum'!F22</f>
-        <v>524552</v>
+        <v>571200</v>
       </c>
       <c r="D23" s="34" t="n">
         <f aca="false">'Lot A - Forum'!F24</f>
-        <v>603234.8</v>
+        <v>656880</v>
       </c>
       <c r="E23" s="25" t="n">
         <f aca="false">ROUND(D23*Summary!$C$9,0)</f>
-        <v>45544227</v>
+        <v>49594440</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2156,7 +2156,7 @@
       <c r="D26" s="21"/>
       <c r="E26" s="21"/>
     </row>
-    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="35" t="s">
         <v>47</v>
       </c>
@@ -2370,19 +2370,19 @@
         <v>71</v>
       </c>
       <c r="E6" s="46" t="n">
-        <v>13000</v>
+        <v>18500</v>
       </c>
       <c r="F6" s="47" t="n">
         <f aca="false">ROUND(C6*E6,2)</f>
-        <v>13000</v>
+        <v>18500</v>
       </c>
       <c r="G6" s="48" t="n">
         <f aca="false">ROUND(E6*Summary!$C$9,0)</f>
-        <v>981500</v>
+        <v>1396750</v>
       </c>
       <c r="H6" s="48" t="n">
         <f aca="false">ROUND(F6*Summary!$C$9,0)</f>
-        <v>981500</v>
+        <v>1396750</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2399,19 +2399,19 @@
         <v>71</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="F7" s="41" t="n">
         <f aca="false">ROUND(C7*E7,2)</f>
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="G7" s="42" t="n">
         <f aca="false">ROUND(E7*Summary!$C$9,0)</f>
-        <v>717250</v>
+        <v>943750</v>
       </c>
       <c r="H7" s="42" t="n">
         <f aca="false">ROUND(F7*Summary!$C$9,0)</f>
-        <v>717250</v>
+        <v>943750</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2428,19 +2428,19 @@
         <v>40</v>
       </c>
       <c r="E8" s="46" t="n">
-        <v>15750</v>
+        <v>19500</v>
       </c>
       <c r="F8" s="47" t="n">
         <f aca="false">ROUND(C8*E8,2)</f>
-        <v>15750</v>
+        <v>19500</v>
       </c>
       <c r="G8" s="48" t="n">
         <f aca="false">ROUND(E8*Summary!$C$9,0)</f>
-        <v>1189125</v>
+        <v>1472250</v>
       </c>
       <c r="H8" s="48" t="n">
         <f aca="false">ROUND(F8*Summary!$C$9,0)</f>
-        <v>1189125</v>
+        <v>1472250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,19 +2457,19 @@
         <v>71</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>8400</v>
+        <v>10500</v>
       </c>
       <c r="F9" s="41" t="n">
         <f aca="false">ROUND(C9*E9,2)</f>
-        <v>8400</v>
+        <v>10500</v>
       </c>
       <c r="G9" s="42" t="n">
         <f aca="false">ROUND(E9*Summary!$C$9,0)</f>
-        <v>634200</v>
+        <v>792750</v>
       </c>
       <c r="H9" s="42" t="n">
         <f aca="false">ROUND(F9*Summary!$C$9,0)</f>
-        <v>634200</v>
+        <v>792750</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2486,19 +2486,19 @@
         <v>71</v>
       </c>
       <c r="E10" s="46" t="n">
-        <v>10800</v>
+        <v>13500</v>
       </c>
       <c r="F10" s="47" t="n">
         <f aca="false">ROUND(C10*E10,2)</f>
-        <v>10800</v>
+        <v>13500</v>
       </c>
       <c r="G10" s="48" t="n">
         <f aca="false">ROUND(E10*Summary!$C$9,0)</f>
-        <v>815400</v>
+        <v>1019250</v>
       </c>
       <c r="H10" s="48" t="n">
         <f aca="false">ROUND(F10*Summary!$C$9,0)</f>
-        <v>815400</v>
+        <v>1019250</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2515,19 +2515,19 @@
         <v>82</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>1025</v>
+        <v>1350</v>
       </c>
       <c r="F11" s="41" t="n">
         <f aca="false">ROUND(C11*E11,2)</f>
-        <v>4100</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="42" t="n">
         <f aca="false">ROUND(E11*Summary!$C$9,0)</f>
-        <v>77388</v>
+        <v>101925</v>
       </c>
       <c r="H11" s="42" t="n">
         <f aca="false">ROUND(F11*Summary!$C$9,0)</f>
-        <v>309550</v>
+        <v>407700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2544,19 +2544,19 @@
         <v>71</v>
       </c>
       <c r="E12" s="46" t="n">
-        <v>19900</v>
+        <v>26500</v>
       </c>
       <c r="F12" s="47" t="n">
         <f aca="false">ROUND(C12*E12,2)</f>
-        <v>19900</v>
+        <v>26500</v>
       </c>
       <c r="G12" s="48" t="n">
         <f aca="false">ROUND(E12*Summary!$C$9,0)</f>
-        <v>1502450</v>
+        <v>2000750</v>
       </c>
       <c r="H12" s="48" t="n">
         <f aca="false">ROUND(F12*Summary!$C$9,0)</f>
-        <v>1502450</v>
+        <v>2000750</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2573,19 +2573,19 @@
         <v>71</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>26500</v>
+        <v>34500</v>
       </c>
       <c r="F13" s="41" t="n">
         <f aca="false">ROUND(C13*E13,2)</f>
-        <v>26500</v>
+        <v>34500</v>
       </c>
       <c r="G13" s="42" t="n">
         <f aca="false">ROUND(E13*Summary!$C$9,0)</f>
-        <v>2000750</v>
+        <v>2604750</v>
       </c>
       <c r="H13" s="42" t="n">
         <f aca="false">ROUND(F13*Summary!$C$9,0)</f>
-        <v>2000750</v>
+        <v>2604750</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2602,19 +2602,19 @@
         <v>82</v>
       </c>
       <c r="E14" s="46" t="n">
-        <v>2400</v>
+        <v>3150</v>
       </c>
       <c r="F14" s="47" t="n">
         <f aca="false">ROUND(C14*E14,2)</f>
-        <v>9600</v>
+        <v>12600</v>
       </c>
       <c r="G14" s="48" t="n">
         <f aca="false">ROUND(E14*Summary!$C$9,0)</f>
-        <v>181200</v>
+        <v>237825</v>
       </c>
       <c r="H14" s="48" t="n">
         <f aca="false">ROUND(F14*Summary!$C$9,0)</f>
-        <v>724800</v>
+        <v>951300</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2631,19 +2631,19 @@
         <v>71</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="41" t="n">
         <f aca="false">ROUND(C15*E15,2)</f>
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="G15" s="42" t="n">
         <f aca="false">ROUND(E15*Summary!$C$9,0)</f>
-        <v>339750</v>
+        <v>377500</v>
       </c>
       <c r="H15" s="42" t="n">
         <f aca="false">ROUND(F15*Summary!$C$9,0)</f>
-        <v>339750</v>
+        <v>377500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2684,19 +2684,19 @@
         <v>71</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="F17" s="41" t="n">
         <f aca="false">ROUND(C17*E17,2)</f>
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="G17" s="42" t="n">
         <f aca="false">ROUND(E17*Summary!$C$9,0)</f>
-        <v>339750</v>
+        <v>415250</v>
       </c>
       <c r="H17" s="42" t="n">
         <f aca="false">ROUND(F17*Summary!$C$9,0)</f>
-        <v>339750</v>
+        <v>415250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2713,19 +2713,19 @@
         <v>71</v>
       </c>
       <c r="E18" s="46" t="n">
-        <v>8500</v>
+        <v>11500</v>
       </c>
       <c r="F18" s="47" t="n">
         <f aca="false">ROUND(C18*E18,2)</f>
-        <v>8500</v>
+        <v>11500</v>
       </c>
       <c r="G18" s="48" t="n">
         <f aca="false">ROUND(E18*Summary!$C$9,0)</f>
-        <v>641750</v>
+        <v>868250</v>
       </c>
       <c r="H18" s="48" t="n">
         <f aca="false">ROUND(F18*Summary!$C$9,0)</f>
-        <v>641750</v>
+        <v>868250</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2742,19 +2742,19 @@
         <v>101</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>830</v>
+        <v>950</v>
       </c>
       <c r="F19" s="41" t="n">
         <f aca="false">ROUND(C19*E19,2)</f>
-        <v>8300</v>
+        <v>9500</v>
       </c>
       <c r="G19" s="42" t="n">
         <f aca="false">ROUND(E19*Summary!$C$9,0)</f>
-        <v>62665</v>
+        <v>71725</v>
       </c>
       <c r="H19" s="42" t="n">
         <f aca="false">ROUND(F19*Summary!$C$9,0)</f>
-        <v>626650</v>
+        <v>717250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2767,12 +2767,12 @@
       <c r="E20" s="52"/>
       <c r="F20" s="53" t="n">
         <f aca="false">SUM(F5:F19)</f>
-        <v>468350</v>
+        <v>510000</v>
       </c>
       <c r="G20" s="54"/>
       <c r="H20" s="55" t="n">
         <f aca="false">ROUND(F20*Summary!$C$9,0)</f>
-        <v>35360425</v>
+        <v>38505000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2785,12 +2785,12 @@
       <c r="E21" s="56"/>
       <c r="F21" s="57" t="n">
         <f aca="false">ROUND(F20*Summary!$C$8,2)</f>
-        <v>56202</v>
+        <v>61200</v>
       </c>
       <c r="G21" s="58"/>
       <c r="H21" s="42" t="n">
         <f aca="false">ROUND(F21*Summary!$C$9,0)</f>
-        <v>4243251</v>
+        <v>4620600</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2803,12 +2803,12 @@
       <c r="E22" s="52"/>
       <c r="F22" s="53" t="n">
         <f aca="false">F20+F21</f>
-        <v>524552</v>
+        <v>571200</v>
       </c>
       <c r="G22" s="54"/>
       <c r="H22" s="55" t="n">
         <f aca="false">ROUND(F22*Summary!$C$9,0)</f>
-        <v>39603676</v>
+        <v>43125600</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2821,12 +2821,12 @@
       <c r="E23" s="56"/>
       <c r="F23" s="57" t="n">
         <f aca="false">ROUND(F22*Summary!$C$7,2)</f>
-        <v>78682.8</v>
+        <v>85680</v>
       </c>
       <c r="G23" s="58"/>
       <c r="H23" s="42" t="n">
         <f aca="false">ROUND(F23*Summary!$C$9,0)</f>
-        <v>5940551</v>
+        <v>6468840</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2839,12 +2839,12 @@
       <c r="E24" s="59"/>
       <c r="F24" s="31" t="n">
         <f aca="false">F22+F23</f>
-        <v>603234.8</v>
+        <v>656880</v>
       </c>
       <c r="G24" s="60"/>
       <c r="H24" s="61" t="n">
         <f aca="false">ROUND(F24*Summary!$C$9,0)</f>
-        <v>45544227</v>
+        <v>49594440</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3574,18 +3574,18 @@
       </c>
       <c r="C6" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F6</f>
-        <v>13000</v>
+        <v>18500</v>
       </c>
       <c r="D6" s="72" t="n">
         <v>10000</v>
       </c>
       <c r="E6" s="71" t="n">
         <f aca="false">C6-D6</f>
-        <v>3000</v>
+        <v>8500</v>
       </c>
       <c r="F6" s="73" t="n">
         <f aca="false">IF(D6=0,"n/a",C6/D6-1)</f>
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>178</v>
@@ -3600,18 +3600,18 @@
       </c>
       <c r="C7" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F7</f>
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="D7" s="72" t="n">
         <v>7400</v>
       </c>
       <c r="E7" s="71" t="n">
         <f aca="false">C7-D7</f>
-        <v>2100</v>
+        <v>5100</v>
       </c>
       <c r="F7" s="73" t="n">
         <f aca="false">IF(D7=0,"n/a",C7/D7-1)</f>
-        <v>0.283783783783784</v>
+        <v>0.689189189189189</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>180</v>
@@ -3626,18 +3626,18 @@
       </c>
       <c r="C8" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F8</f>
-        <v>15750</v>
+        <v>19500</v>
       </c>
       <c r="D8" s="72" t="n">
         <v>12250</v>
       </c>
       <c r="E8" s="71" t="n">
         <f aca="false">C8-D8</f>
-        <v>3500</v>
+        <v>7250</v>
       </c>
       <c r="F8" s="73" t="n">
         <f aca="false">IF(D8=0,"n/a",C8/D8-1)</f>
-        <v>0.285714285714286</v>
+        <v>0.591836734693878</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>182</v>
@@ -3652,18 +3652,18 @@
       </c>
       <c r="C9" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F9</f>
-        <v>8400</v>
+        <v>10500</v>
       </c>
       <c r="D9" s="72" t="n">
         <v>6500</v>
       </c>
       <c r="E9" s="71" t="n">
         <f aca="false">C9-D9</f>
-        <v>1900</v>
+        <v>4000</v>
       </c>
       <c r="F9" s="73" t="n">
         <f aca="false">IF(D9=0,"n/a",C9/D9-1)</f>
-        <v>0.292307692307692</v>
+        <v>0.615384615384615</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>184</v>
@@ -3678,18 +3678,18 @@
       </c>
       <c r="C10" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F10</f>
-        <v>10800</v>
+        <v>13500</v>
       </c>
       <c r="D10" s="72" t="n">
         <v>8500</v>
       </c>
       <c r="E10" s="71" t="n">
         <f aca="false">C10-D10</f>
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="F10" s="73" t="n">
         <f aca="false">IF(D10=0,"n/a",C10/D10-1)</f>
-        <v>0.270588235294118</v>
+        <v>0.588235294117647</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>186</v>
@@ -3704,18 +3704,18 @@
       </c>
       <c r="C11" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F11</f>
-        <v>4100</v>
+        <v>5400</v>
       </c>
       <c r="D11" s="72" t="n">
         <v>3200</v>
       </c>
       <c r="E11" s="71" t="n">
         <f aca="false">C11-D11</f>
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="F11" s="73" t="n">
         <f aca="false">IF(D11=0,"n/a",C11/D11-1)</f>
-        <v>0.28125</v>
+        <v>0.6875</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>188</v>
@@ -3730,18 +3730,18 @@
       </c>
       <c r="C12" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F12</f>
-        <v>19900</v>
+        <v>26500</v>
       </c>
       <c r="D12" s="72" t="n">
         <v>15500</v>
       </c>
       <c r="E12" s="71" t="n">
         <f aca="false">C12-D12</f>
-        <v>4400</v>
+        <v>11000</v>
       </c>
       <c r="F12" s="73" t="n">
         <f aca="false">IF(D12=0,"n/a",C12/D12-1)</f>
-        <v>0.283870967741936</v>
+        <v>0.709677419354839</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>190</v>
@@ -3756,18 +3756,18 @@
       </c>
       <c r="C13" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F13</f>
-        <v>26500</v>
+        <v>34500</v>
       </c>
       <c r="D13" s="72" t="n">
         <v>20500</v>
       </c>
       <c r="E13" s="71" t="n">
         <f aca="false">C13-D13</f>
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="F13" s="73" t="n">
         <f aca="false">IF(D13=0,"n/a",C13/D13-1)</f>
-        <v>0.292682926829268</v>
+        <v>0.682926829268293</v>
       </c>
       <c r="G13" s="26" t="s">
         <v>192</v>
@@ -3782,18 +3782,18 @@
       </c>
       <c r="C14" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F14</f>
-        <v>9600</v>
+        <v>12600</v>
       </c>
       <c r="D14" s="72" t="n">
         <v>6300</v>
       </c>
       <c r="E14" s="71" t="n">
         <f aca="false">C14-D14</f>
-        <v>3300</v>
+        <v>6300</v>
       </c>
       <c r="F14" s="73" t="n">
         <f aca="false">IF(D14=0,"n/a",C14/D14-1)</f>
-        <v>0.523809523809524</v>
+        <v>1</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>194</v>
@@ -3808,18 +3808,18 @@
       </c>
       <c r="C15" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F15</f>
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="D15" s="72" t="n">
         <v>2800</v>
       </c>
       <c r="E15" s="71" t="n">
         <f aca="false">C15-D15</f>
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="F15" s="73" t="n">
         <f aca="false">IF(D15=0,"n/a",C15/D15-1)</f>
-        <v>0.607142857142857</v>
+        <v>0.785714285714286</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>196</v>
@@ -3834,18 +3834,18 @@
       </c>
       <c r="C16" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F17</f>
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="D16" s="72" t="n">
         <v>2500</v>
       </c>
       <c r="E16" s="71" t="n">
         <f aca="false">C16-D16</f>
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F16" s="73" t="n">
         <f aca="false">IF(D16=0,"n/a",C16/D16-1)</f>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>198</v>
@@ -3860,18 +3860,18 @@
       </c>
       <c r="C17" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F18</f>
-        <v>8500</v>
+        <v>11500</v>
       </c>
       <c r="D17" s="72" t="n">
         <v>6000</v>
       </c>
       <c r="E17" s="71" t="n">
         <f aca="false">C17-D17</f>
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F17" s="73" t="n">
         <f aca="false">IF(D17=0,"n/a",C17/D17-1)</f>
-        <v>0.416666666666667</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>200</v>
@@ -3886,18 +3886,18 @@
       </c>
       <c r="C18" s="71" t="n">
         <f aca="false">'Lot A - Forum'!F19</f>
-        <v>8300</v>
+        <v>9500</v>
       </c>
       <c r="D18" s="72" t="n">
         <v>6500</v>
       </c>
       <c r="E18" s="71" t="n">
         <f aca="false">C18-D18</f>
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="F18" s="73" t="n">
         <f aca="false">IF(D18=0,"n/a",C18/D18-1)</f>
-        <v>0.276923076923077</v>
+        <v>0.461538461538461</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>202</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="C25" s="75" t="n">
         <f aca="false">SUM(C5:C24)</f>
-        <v>786030</v>
+        <v>827680</v>
       </c>
       <c r="D25" s="75" t="n">
         <f aca="false">SUM(D5:D24)</f>
@@ -4074,11 +4074,11 @@
       </c>
       <c r="E25" s="75" t="n">
         <f aca="false">C25-D25</f>
-        <v>176525</v>
+        <v>218175</v>
       </c>
       <c r="F25" s="76" t="n">
         <f aca="false">IF(D25=0,"n/a",C25/D25-1)</f>
-        <v>0.289620265625385</v>
+        <v>0.357954405624236</v>
       </c>
       <c r="G25" s="54"/>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C26" s="78" t="n">
         <f aca="false">'Lot A - Forum'!F21+'Lot B - Pavilion'!F12</f>
-        <v>94323.6</v>
+        <v>99321.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
